--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\szubair\Projects\Automation\Selenium_Automation\Selenium_POM\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\szubair\Projects\Automation\Selenium_POM_DD\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C40AE08-E2C3-472A-A674-67B9034704B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82FE328-E801-4F5D-A385-428D666A4AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GlobalConfig" sheetId="2" r:id="rId1"/>
+    <sheet name="GlobalConfig" sheetId="7" r:id="rId1"/>
     <sheet name="TEST SUMMARY" sheetId="3" r:id="rId2"/>
-    <sheet name="Add_To_Cart_TC001" sheetId="6" r:id="rId3"/>
-    <sheet name="Valid_Login_TC001" sheetId="1" r:id="rId4"/>
-    <sheet name="MyAccount_TC001" sheetId="5" r:id="rId5"/>
-    <sheet name="InValid_Login_TC002" sheetId="4" r:id="rId6"/>
+    <sheet name="Valid_Login_TC001" sheetId="1" r:id="rId3"/>
+    <sheet name="Add_To_Cart_TC001" sheetId="6" r:id="rId4"/>
+    <sheet name="InValid_Login_TC002" sheetId="4" r:id="rId5"/>
+    <sheet name="MyAccount_TC001" sheetId="5" r:id="rId6"/>
+    <sheet name="Modify_Address_TC001" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="89">
   <si>
     <t>UserName</t>
   </si>
@@ -215,13 +216,88 @@
     <t>Click on Mac (1)</t>
   </si>
   <si>
-    <t>Verify the text 'Mac'</t>
-  </si>
-  <si>
     <t>Click on 'Add to Cart'</t>
   </si>
   <si>
     <t>Verify text ' Success: You have added '</t>
+  </si>
+  <si>
+    <t>STEP 20</t>
+  </si>
+  <si>
+    <t>STEP 22</t>
+  </si>
+  <si>
+    <t>Click on 'Modify your address book entries'</t>
+  </si>
+  <si>
+    <t>Verify the text 'Address Book Entries'</t>
+  </si>
+  <si>
+    <t>Click on 'New Address' button</t>
+  </si>
+  <si>
+    <t>Vreify the text 'Add Address'</t>
+  </si>
+  <si>
+    <t>Enter Address 1</t>
+  </si>
+  <si>
+    <t>Enter City</t>
+  </si>
+  <si>
+    <t>Enter post code</t>
+  </si>
+  <si>
+    <t>Select country as 'India'</t>
+  </si>
+  <si>
+    <t>Select region state as 'Telangana'</t>
+  </si>
+  <si>
+    <t>STEP 19</t>
+  </si>
+  <si>
+    <t>STEP 21</t>
+  </si>
+  <si>
+    <t>Click on contnue button</t>
+  </si>
+  <si>
+    <t>Verify the text ' Your address has been successfully added'</t>
+  </si>
+  <si>
+    <t>Modify_Address_TC001</t>
+  </si>
+  <si>
+    <t>Verify the text 'Address has been deleted successfully'</t>
+  </si>
+  <si>
+    <t>STEP 23</t>
+  </si>
+  <si>
+    <t>Click on Delete button</t>
+  </si>
+  <si>
+    <t>STEP 24</t>
+  </si>
+  <si>
+    <t>Click on 'Shopping cart link'</t>
+  </si>
+  <si>
+    <t>Verify 'Checkout' button is enabled</t>
+  </si>
+  <si>
+    <t>Click on delete product button</t>
+  </si>
+  <si>
+    <t>Click on logout</t>
+  </si>
+  <si>
+    <t>Add_To_Cart_TC001</t>
+  </si>
+  <si>
+    <t>Verify text 'Your shopping cart is empty!'</t>
   </si>
 </sst>
 </file>
@@ -570,12 +646,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81751ACE-26ED-4BEC-8C39-8E42D04D3AC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E81577-1549-416F-BD24-273D0BFE2309}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -620,9 +696,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{76E6B4C9-E487-4905-A421-41FFE9C406DA}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{938D1F99-3934-45A9-BF06-BAC0C768DFAC}"/>
-    <hyperlink ref="B4" r:id="rId3" display="Sy@Ed4#4" xr:uid="{E13D6C8B-0D40-41C4-B0EA-4E199D046F7F}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{DE454AEA-5466-4A7C-9470-285ADBC9711E}"/>
+    <hyperlink ref="B4" r:id="rId2" display="Sy@Ed4#4" xr:uid="{5B7D18F3-0563-442B-8394-784BD1F4170C}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{9AE62AB3-C00C-4D10-9D5C-CE7F93D7376D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -630,10 +706,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFA151F-FAEC-462B-9584-CD0FCD1F90CF}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.453125" customWidth="1"/>
     <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
@@ -674,190 +750,22 @@
         <v>40</v>
       </c>
     </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFB7898-F58F-4AFA-9F8C-5AE91DE785B9}">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -988,7 +896,306 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFB7898-F58F-4AFA-9F8C-5AE91DE785B9}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{818959B1-0F61-4CB7-9252-3FDC54942479}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7439856E-4C7C-4E8E-85E3-D6308FD46250}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1165,17 +1372,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{818959B1-0F61-4CB7-9252-3FDC54942479}">
-  <dimension ref="A1:E10"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9CA027-9520-4AB8-A443-500C24750815}">
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" customWidth="1"/>
+    <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1261,10 +1469,131 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>